--- a/18-03-01/raspis-v3--31-08-2026/raspisanie-152-v1-31-08-2026.xlsx
+++ b/18-03-01/raspis-v3--31-08-2026/raspisanie-152-v1-31-08-2026.xlsx
@@ -3,15 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BC81C37-2A59-4AD4-9EB5-087FAD8D208B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77771D36-BC7D-4415-B323-C82E4765645A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="template" sheetId="5" r:id="rId1"/>
     <sheet name="info" sheetId="4" r:id="rId2"/>
-    <sheet name="template-odd" sheetId="6" r:id="rId3"/>
-    <sheet name="template-even" sheetId="7" r:id="rId4"/>
+    <sheet name="template-even" sheetId="6" r:id="rId3"/>
+    <sheet name="template-odd" sheetId="7" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -145,12 +145,6 @@
     <t>7-317</t>
   </si>
   <si>
-    <t>Чётная неделя (?)</t>
-  </si>
-  <si>
-    <t>Нечётная неделя (?)</t>
-  </si>
-  <si>
     <t>Введение в химическую технологию и основы научных исследований</t>
   </si>
   <si>
@@ -227,6 +221,12 @@
   </si>
   <si>
     <t>Погребная Л.И.</t>
+  </si>
+  <si>
+    <t>Нечётная неделя</t>
+  </si>
+  <si>
+    <t>Чётная неделя</t>
   </si>
 </sst>
 </file>
@@ -1527,13 +1527,13 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
         <v>27</v>
@@ -1542,7 +1542,7 @@
         <v>23</v>
       </c>
       <c r="F2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G2" s="1">
         <v>0.39583333333333331</v>
@@ -1553,13 +1553,13 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
         <v>21</v>
@@ -1568,7 +1568,7 @@
         <v>25</v>
       </c>
       <c r="F3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G3" s="1">
         <v>0.47916666666666669</v>
@@ -1582,7 +1582,7 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D4" t="s">
         <v>26</v>
@@ -1591,7 +1591,7 @@
         <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G4" s="1">
         <v>0.58333333333333337</v>
@@ -1605,7 +1605,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E5" t="s">
         <v>32</v>
@@ -1625,13 +1625,13 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E6">
         <v>206</v>
       </c>
       <c r="F6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G6" s="2">
         <v>0.75</v>
@@ -1648,12 +1648,12 @@
         <v>13</v>
       </c>
       <c r="F7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E8" t="s">
         <v>33</v>
@@ -1664,46 +1664,46 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E9" t="s">
         <v>28</v>
       </c>
       <c r="F9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E10" t="s">
         <v>24</v>
       </c>
       <c r="F10" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E11">
         <v>201</v>
       </c>
       <c r="F11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E12">
         <v>254</v>
       </c>
       <c r="F12" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
@@ -1711,7 +1711,7 @@
         <v>34</v>
       </c>
       <c r="F13" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
@@ -1719,7 +1719,7 @@
         <v>35</v>
       </c>
       <c r="F14" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
@@ -1727,7 +1727,7 @@
         <v>36</v>
       </c>
       <c r="F15" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
@@ -1735,17 +1735,17 @@
         <v>37</v>
       </c>
       <c r="F16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="5:6" x14ac:dyDescent="0.3">
       <c r="F17" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E19" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="5:6" x14ac:dyDescent="0.3">
@@ -1790,7 +1790,7 @@
     </row>
     <row r="28" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E28" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29" spans="5:6" x14ac:dyDescent="0.3">
@@ -1850,7 +1850,7 @@
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="44" t="str">
         <f>info!A3</f>
-        <v>Нечётная неделя (?)</v>
+        <v>Чётная неделя</v>
       </c>
       <c r="B1" s="45"/>
       <c r="C1" s="45"/>
@@ -2576,7 +2576,7 @@
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="44" t="str">
         <f>info!A2</f>
-        <v>Чётная неделя (?)</v>
+        <v>Нечётная неделя</v>
       </c>
       <c r="B1" s="45"/>
       <c r="C1" s="45"/>

--- a/18-03-01/raspis-v3--31-08-2026/raspisanie-152-v1-31-08-2026.xlsx
+++ b/18-03-01/raspis-v3--31-08-2026/raspisanie-152-v1-31-08-2026.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77771D36-BC7D-4415-B323-C82E4765645A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{983AAD8C-F178-42C8-BA87-54B1747ADCA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="62">
   <si>
     <t>Пара</t>
   </si>
@@ -70,9 +70,6 @@
     <t>Пятница</t>
   </si>
   <si>
-    <t>7-119</t>
-  </si>
-  <si>
     <t>предмет</t>
   </si>
   <si>
@@ -103,9 +100,6 @@
     <t>Каф. ин.яз.</t>
   </si>
   <si>
-    <t>Каф. САиИТ</t>
-  </si>
-  <si>
     <t>Каф. физвоспит.</t>
   </si>
   <si>
@@ -115,9 +109,6 @@
     <t>Лекц.</t>
   </si>
   <si>
-    <t>7-322</t>
-  </si>
-  <si>
     <t>Винник Т.В.</t>
   </si>
   <si>
@@ -130,21 +121,9 @@
     <t>БХА</t>
   </si>
   <si>
-    <t>7-212</t>
-  </si>
-  <si>
-    <t>БФА</t>
-  </si>
-  <si>
-    <t>Каф. инж. проект.</t>
-  </si>
-  <si>
     <t>7-320</t>
   </si>
   <si>
-    <t>7-317</t>
-  </si>
-  <si>
     <t>Введение в химическую технологию и основы научных исследований</t>
   </si>
   <si>
@@ -208,9 +187,6 @@
     <t>Каф.</t>
   </si>
   <si>
-    <t>1(118)</t>
-  </si>
-  <si>
     <t>Галуза Л.Н.</t>
   </si>
   <si>
@@ -227,6 +203,18 @@
   </si>
   <si>
     <t>Чётная неделя</t>
+  </si>
+  <si>
+    <t>7-401</t>
+  </si>
+  <si>
+    <t>7-118</t>
+  </si>
+  <si>
+    <t>7-326</t>
+  </si>
+  <si>
+    <t>7-325</t>
   </si>
 </sst>
 </file>
@@ -1501,48 +1489,48 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="40" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B1" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="40" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="40" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="40" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="40" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" s="40" t="s">
-        <v>17</v>
-      </c>
-      <c r="G1" s="40" t="s">
+      <c r="H1" s="40" t="s">
         <v>19</v>
-      </c>
-      <c r="H1" s="40" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="G2" s="1">
         <v>0.39583333333333331</v>
@@ -1553,22 +1541,22 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F3" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G3" s="1">
         <v>0.47916666666666669</v>
@@ -1582,16 +1570,16 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F4" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G4" s="1">
         <v>0.58333333333333337</v>
@@ -1605,13 +1593,13 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G5" s="1">
         <v>0.66666666666666663</v>
@@ -1625,13 +1613,10 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E6">
-        <v>206</v>
+        <v>37</v>
       </c>
       <c r="F6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G6" s="2">
         <v>0.75</v>
@@ -1644,108 +1629,78 @@
       <c r="C7" t="s">
         <v>8</v>
       </c>
-      <c r="E7" t="s">
-        <v>13</v>
-      </c>
       <c r="F7" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E8" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F8" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
-        <v>50</v>
-      </c>
-      <c r="E9" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="F9" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
-        <v>51</v>
-      </c>
-      <c r="E10" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="F10" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
-        <v>55</v>
-      </c>
-      <c r="E11">
-        <v>201</v>
+        <v>48</v>
       </c>
       <c r="F11" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C12" t="s">
-        <v>57</v>
-      </c>
-      <c r="E12">
-        <v>254</v>
+        <v>50</v>
       </c>
       <c r="F12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F13" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F14" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F15" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="E13" t="s">
-        <v>34</v>
-      </c>
-      <c r="F13" t="s">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F16" t="s">
         <v>54</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="E14" t="s">
-        <v>35</v>
-      </c>
-      <c r="F14" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="E15" t="s">
-        <v>36</v>
-      </c>
-      <c r="F15" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="E16" t="s">
-        <v>37</v>
-      </c>
-      <c r="F16" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="17" spans="5:6" x14ac:dyDescent="0.3">
       <c r="F17" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E19" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="5:6" x14ac:dyDescent="0.3">
@@ -1754,8 +1709,8 @@
       </c>
     </row>
     <row r="21" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E21">
-        <v>326</v>
+      <c r="E21" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="5:6" x14ac:dyDescent="0.3">
@@ -1764,8 +1719,8 @@
       </c>
     </row>
     <row r="23" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E23">
-        <v>401</v>
+      <c r="E23" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="5:6" x14ac:dyDescent="0.3">
@@ -1775,7 +1730,7 @@
     </row>
     <row r="25" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E25" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="5:6" x14ac:dyDescent="0.3">
@@ -1784,8 +1739,8 @@
       </c>
     </row>
     <row r="27" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E27">
-        <v>319</v>
+      <c r="E27" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="28" spans="5:6" x14ac:dyDescent="0.3">
@@ -1794,13 +1749,13 @@
       </c>
     </row>
     <row r="29" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E29">
-        <v>320</v>
+      <c r="E29" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E30">
-        <v>413</v>
+      <c r="E30" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="5:6" x14ac:dyDescent="0.3">
@@ -1970,22 +1925,10 @@
       <c r="B6" s="29">
         <v>4</v>
       </c>
-      <c r="C6" s="13" t="str">
-        <f>info!C11</f>
-        <v>Физическая подготовка</v>
-      </c>
-      <c r="D6" s="13" t="str">
-        <f>info!D4</f>
-        <v>Практ.</v>
-      </c>
-      <c r="E6" s="13" t="str">
-        <f>info!E19</f>
-        <v>Каф.</v>
-      </c>
-      <c r="F6" s="13" t="str">
-        <f>info!F4</f>
-        <v>Неопределен</v>
-      </c>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
       <c r="G6" s="14">
         <f>info!G5</f>
         <v>0.66666666666666663</v>
@@ -2047,9 +1990,9 @@
         <f>info!D4</f>
         <v>Практ.</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="9" t="str">
         <f>info!E21</f>
-        <v>326</v>
+        <v>7-326</v>
       </c>
       <c r="F9" s="9" t="str">
         <f>info!F6</f>
@@ -2158,9 +2101,9 @@
         <f>info!D2</f>
         <v>Лекц.</v>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="20" t="str">
         <f>info!E23</f>
-        <v>401</v>
+        <v>7-401</v>
       </c>
       <c r="F13" s="20" t="str">
         <f>info!F5</f>
@@ -2188,9 +2131,9 @@
         <f>info!D2</f>
         <v>Лекц.</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="13" t="str">
         <f>info!E30</f>
-        <v>413</v>
+        <v>7-413</v>
       </c>
       <c r="F14" s="13" t="str">
         <f>info!F10</f>
@@ -2377,9 +2320,9 @@
         <f>info!D4</f>
         <v>Практ.</v>
       </c>
-      <c r="E21" s="9">
-        <f>info!E33</f>
-        <v>319</v>
+      <c r="E21" s="9" t="str">
+        <f>info!E27</f>
+        <v>7-325</v>
       </c>
       <c r="F21" s="9" t="str">
         <f>info!F12</f>
@@ -2450,10 +2393,22 @@
       <c r="B24" s="29">
         <v>2</v>
       </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
+      <c r="C24" s="13" t="str">
+        <f>info!C11</f>
+        <v>Физическая подготовка</v>
+      </c>
+      <c r="D24" s="13" t="str">
+        <f>info!D4</f>
+        <v>Практ.</v>
+      </c>
+      <c r="E24" s="13" t="str">
+        <f>info!E19</f>
+        <v>Каф.</v>
+      </c>
+      <c r="F24" s="13" t="str">
+        <f>info!F4</f>
+        <v>Неопределен</v>
+      </c>
       <c r="G24" s="14">
         <f>info!G3</f>
         <v>0.47916666666666669</v>
@@ -2508,7 +2463,7 @@
       </c>
       <c r="E26" s="13" t="str">
         <f>info!E28</f>
-        <v>1(118)</v>
+        <v>7-118</v>
       </c>
       <c r="F26" s="13" t="str">
         <f>info!F5</f>
@@ -2755,9 +2710,9 @@
         <f>info!D4</f>
         <v>Практ.</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="6" t="str">
         <f>info!E29</f>
-        <v>320</v>
+        <v>7-320</v>
       </c>
       <c r="F8" s="6" t="str">
         <f>info!F6</f>
@@ -2785,9 +2740,9 @@
         <f>info!D2</f>
         <v>Лекц.</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="9" t="str">
         <f>info!E30</f>
-        <v>413</v>
+        <v>7-413</v>
       </c>
       <c r="F9" s="9" t="str">
         <f>info!F14</f>
@@ -3115,9 +3070,9 @@
         <f>info!D4</f>
         <v>Практ.</v>
       </c>
-      <c r="E21" s="9">
+      <c r="E21" s="9" t="str">
         <f>info!E27</f>
-        <v>319</v>
+        <v>7-325</v>
       </c>
       <c r="F21" s="9" t="str">
         <f>info!F12</f>
@@ -3258,7 +3213,7 @@
       </c>
       <c r="E26" s="13" t="str">
         <f>info!E28</f>
-        <v>1(118)</v>
+        <v>7-118</v>
       </c>
       <c r="F26" s="13" t="str">
         <f>info!F5</f>
